--- a/artfynd/A 18106-2024 artfynd.xlsx
+++ b/artfynd/A 18106-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753449</v>
+        <v>117753450</v>
       </c>
       <c r="B5" t="n">
         <v>90517</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421076</v>
+        <v>421197</v>
       </c>
       <c r="R5" t="n">
-        <v>7053699</v>
+        <v>7053615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117753458</v>
+        <v>117753448</v>
       </c>
       <c r="B6" t="n">
-        <v>86816</v>
+        <v>90517</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,21 +1168,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>420759</v>
+        <v>420674</v>
       </c>
       <c r="R6" t="n">
-        <v>7053677</v>
+        <v>7053627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117753367</v>
+        <v>117753447</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>90513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,21 +1270,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>420576</v>
+        <v>420628</v>
       </c>
       <c r="R7" t="n">
-        <v>7053815</v>
+        <v>7053608</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,11 +1330,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,7 +1356,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117753448</v>
+        <v>117753449</v>
       </c>
       <c r="B8" t="n">
         <v>90517</v>
@@ -1401,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>420674</v>
+        <v>421076</v>
       </c>
       <c r="R8" t="n">
-        <v>7053627</v>
+        <v>7053699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1463,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117753450</v>
+        <v>117753458</v>
       </c>
       <c r="B9" t="n">
-        <v>90517</v>
+        <v>86816</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1474,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421197</v>
+        <v>420759</v>
       </c>
       <c r="R9" t="n">
-        <v>7053615</v>
+        <v>7053677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117753447</v>
+        <v>117753367</v>
       </c>
       <c r="B10" t="n">
-        <v>90513</v>
+        <v>57287</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,21 +1576,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1605,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>420628</v>
+        <v>420576</v>
       </c>
       <c r="R10" t="n">
-        <v>7053608</v>
+        <v>7053815</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,6 +1636,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 18106-2024 artfynd.xlsx
+++ b/artfynd/A 18106-2024 artfynd.xlsx
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753450</v>
+        <v>117753449</v>
       </c>
       <c r="B5" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421197</v>
+        <v>421076</v>
       </c>
       <c r="R5" t="n">
-        <v>7053615</v>
+        <v>7053699</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1155,7 +1155,7 @@
         <v>117753448</v>
       </c>
       <c r="B6" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117753447</v>
+        <v>117753367</v>
       </c>
       <c r="B7" t="n">
-        <v>90513</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,21 +1270,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>420628</v>
+        <v>420576</v>
       </c>
       <c r="R7" t="n">
-        <v>7053608</v>
+        <v>7053815</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,6 +1330,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117753449</v>
+        <v>117753458</v>
       </c>
       <c r="B8" t="n">
-        <v>90517</v>
+        <v>86818</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421076</v>
+        <v>420759</v>
       </c>
       <c r="R8" t="n">
-        <v>7053699</v>
+        <v>7053677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117753458</v>
+        <v>117753450</v>
       </c>
       <c r="B9" t="n">
-        <v>86816</v>
+        <v>90519</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,21 +1479,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420759</v>
+        <v>421197</v>
       </c>
       <c r="R9" t="n">
-        <v>7053677</v>
+        <v>7053615</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117753367</v>
+        <v>117753447</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>90515</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,21 +1581,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1600,10 +1605,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>420576</v>
+        <v>420628</v>
       </c>
       <c r="R10" t="n">
-        <v>7053815</v>
+        <v>7053608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,11 +1641,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
